--- a/data/trans_dic/IP2003-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que tienen dientes o muelas empastados</t>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,8; 20,33</t>
+          <t>8,86; 20,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,3; 28,45</t>
+          <t>12,99; 28,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,81; 25,03</t>
+          <t>9,73; 24,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,64; 17,62</t>
+          <t>7,06; 17,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,75; 22,95</t>
+          <t>9,88; 21,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 15,21</t>
+          <t>4,77; 14,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,49; 22,22</t>
+          <t>9,37; 21,96</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,3; 16,59</t>
+          <t>6,21; 15,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,52; 18,78</t>
+          <t>10,7; 19,07</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,23; 19,48</t>
+          <t>10,36; 19,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,56; 21,6</t>
+          <t>11,5; 21,08</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,56; 14,84</t>
+          <t>7,68; 14,63</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,51; 19,13</t>
+          <t>6,54; 19,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 24,22</t>
+          <t>10,09; 23,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 15,89</t>
+          <t>5,82; 16,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,37; 21,09</t>
+          <t>8,32; 20,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,13; 17,31</t>
+          <t>6,09; 17,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 16,19</t>
+          <t>5,77; 17,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 13,64</t>
+          <t>4,85; 14,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,23; 22,3</t>
+          <t>9,48; 22,77</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 15,41</t>
+          <t>7,47; 15,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,61; 17,41</t>
+          <t>9,39; 17,71</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,32; 13,15</t>
+          <t>6,05; 13,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 19,2</t>
+          <t>10,56; 19,17</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,37; 20,95</t>
+          <t>7,46; 20,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,81; 25,63</t>
+          <t>11,68; 25,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,21; 18,54</t>
+          <t>4,4; 18,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 22,42</t>
+          <t>6,42; 21,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,4; 21,34</t>
+          <t>9,01; 20,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,77; 21,27</t>
+          <t>8,48; 21,04</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 17,21</t>
+          <t>4,2; 16,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 21,88</t>
+          <t>4,87; 23,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,84; 18,66</t>
+          <t>9,68; 18,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,96; 21,18</t>
+          <t>11,87; 21,39</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,7; 14,19</t>
+          <t>5,39; 14,22</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 18,71</t>
+          <t>6,85; 19,03</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,36; 19,9</t>
+          <t>11,58; 19,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 18,59</t>
+          <t>10,32; 18,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,84; 18,71</t>
+          <t>10,96; 18,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,47; 52,43</t>
+          <t>11,68; 56,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,6; 18,75</t>
+          <t>10,62; 19,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 16,21</t>
+          <t>8,98; 16,35</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,85; 17,85</t>
+          <t>10,12; 18,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,46; 24,46</t>
+          <t>12,3; 25,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,05; 17,93</t>
+          <t>12,27; 18,12</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,63; 16,25</t>
+          <t>10,61; 16,14</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 16,87</t>
+          <t>11,28; 17,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 38,7</t>
+          <t>13,66; 36,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,39; 32,82</t>
+          <t>18,28; 33,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,14; 25,75</t>
+          <t>14,13; 24,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 20,62</t>
+          <t>10,39; 20,47</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,48; 30,5</t>
+          <t>14,58; 30,22</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,86; 23,27</t>
+          <t>12,87; 24,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,55; 22,81</t>
+          <t>11,45; 22,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,36; 21,26</t>
+          <t>10,28; 20,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,81; 35,29</t>
+          <t>8,99; 35,59</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,11; 25,98</t>
+          <t>17,17; 25,48</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,2; 22,0</t>
+          <t>14,63; 22,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,59; 19,15</t>
+          <t>11,53; 18,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,57; 30,64</t>
+          <t>13,14; 29,32</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,94; 28,08</t>
+          <t>12,08; 27,68</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,95; 23,4</t>
+          <t>6,82; 21,87</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,22; 27,96</t>
+          <t>10,25; 27,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,25; 14,1</t>
+          <t>3,31; 13,5</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 11,06</t>
+          <t>1,98; 11,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,94; 24,99</t>
+          <t>10,41; 24,85</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,3; 21,96</t>
+          <t>8,08; 24,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,33; 16,82</t>
+          <t>2,71; 16,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,63; 18,17</t>
+          <t>8,78; 18,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,56; 22,02</t>
+          <t>11,02; 21,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,64; 21,58</t>
+          <t>10,57; 21,96</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 12,03</t>
+          <t>4,16; 12,09</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,11; 18,97</t>
+          <t>13,94; 18,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,45</t>
+          <t>14,43; 19,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,67; 16,45</t>
+          <t>11,72; 16,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,91; 31,75</t>
+          <t>12,54; 29,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,64; 15,99</t>
+          <t>11,64; 16,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,1; 15,46</t>
+          <t>11,11; 15,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,79; 15,19</t>
+          <t>10,48; 15,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,49; 19,6</t>
+          <t>11,33; 18,89</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,47; 16,85</t>
+          <t>13,46; 16,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,31; 16,58</t>
+          <t>13,3; 16,45</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,78; 15,06</t>
+          <t>11,84; 14,9</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,06; 21,5</t>
+          <t>13,0; 21,74</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen dientes o muelas empastados (tasa de respuesta: 99,85%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>13380</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>16425</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>12729</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11880</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>13764</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14185</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>27235</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>23701</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26494</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>26065</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>8536; 19547</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10823; 23795</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7515; 19277</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>7286; 18476</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>9058; 20093</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3942; 12311</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>8451; 19799</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8449; 21716</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>20121; 35869</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>17191; 31878</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>19248; 35285</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>18381; 35022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>9443</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9914</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>12855</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>8919</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>9495</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13970</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>18362</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23788</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>18765</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>26825</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>5333; 15629</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>8751; 20437</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>5685; 15805</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>7876; 19126</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5014; 14227</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>5315; 15725</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5117; 15365</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8840; 21228</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>12245; 25948</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>16794; 31673</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>12296; 27488</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>19845; 36020</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>8418</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>14459</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>5458</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6305</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>13896</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>11645</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>7231</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>22314</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>26103</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>12024</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>13537</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>4822; 13478</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>9489; 20537</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2541; 10484</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>3203; 10876</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>8812; 20368</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6972; 17306</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2971; 11602</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3077; 14577</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>15732; 29743</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>19405; 34973</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>6932; 18271</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>7746; 21512</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>29075</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>27134</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>29482</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>51580</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>27339</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>25581</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>27327</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>36515</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>56414</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>52715</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>56808</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>88095</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>22190; 37923</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>19653; 35992</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>22775; 38865</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24985; 121787</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>20082; 36302</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>18921; 34436</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>20551; 36680</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>26147; 54751</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>46718; 68992</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>42557; 64702</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>46337; 69920</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>58255; 155143</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>25228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>26607</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>19748</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>24954</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21490</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21571</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>20081</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>26949</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>46718</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>48177</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>39828</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>51903</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>18308; 33443</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19561; 34595</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13597; 26795</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>17108; 35464</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>15655; 29299</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>15071; 29526</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>13886; 27742</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>14349; 56779</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>38084; 56509</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>39516; 59414</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>30675; 50054</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>36388; 81175</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>13982</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>6614</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9853</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>11663</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>9134</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>5502</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>17302</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>18277</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>18988</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>10343</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>8644; 19801</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3402; 10911</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>5812; 15315</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2280; 9303</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1302; 7253</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>7151; 17062</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>5254; 15644</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>1906; 11441</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>12055; 24780</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>13070; 25522</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>12860; 26719</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>5792; 16845</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>99526</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>105530</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>87184</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>112415</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>88819</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>87231</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>85723</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>104352</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>188344</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>192761</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>172907</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>216767</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>84470; 115104</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>90892; 122054</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>73616; 102829</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>81275; 190321</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>75476; 104569</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>74191; 102489</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>70178; 101803</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>83306; 138880</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>168876; 208258</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>172629; 213536</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>153613; 193312</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>179830; 300741</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP2003-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,86; 20,28</t>
+          <t>8,87; 20,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,99; 28,55</t>
+          <t>12,28; 27,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,73; 24,95</t>
+          <t>9,4; 24,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,06; 17,89</t>
+          <t>6,86; 17,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,88; 21,92</t>
+          <t>9,53; 21,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,77; 14,9</t>
+          <t>4,6; 15,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 21,96</t>
+          <t>9,67; 22,57</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,21; 15,95</t>
+          <t>6,25; 16,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 19,07</t>
+          <t>10,63; 18,75</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 19,21</t>
+          <t>10,13; 19,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,5; 21,08</t>
+          <t>11,57; 20,9</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 14,63</t>
+          <t>7,68; 15,09</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,54; 19,16</t>
+          <t>6,09; 17,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,09; 23,56</t>
+          <t>10,7; 24,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,82; 16,18</t>
+          <t>5,96; 16,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,32; 20,2</t>
+          <t>8,46; 20,29</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 17,27</t>
+          <t>5,87; 17,61</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 17,08</t>
+          <t>6,06; 16,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 14,56</t>
+          <t>4,65; 13,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,48; 22,77</t>
+          <t>8,95; 22,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,47; 15,83</t>
+          <t>7,57; 15,93</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,39; 17,71</t>
+          <t>9,62; 17,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 13,53</t>
+          <t>6,03; 12,6</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,56; 19,17</t>
+          <t>10,25; 19,04</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 20,84</t>
+          <t>7,86; 20,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,68; 25,28</t>
+          <t>11,83; 26,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,4; 18,17</t>
+          <t>4,5; 17,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,42; 21,79</t>
+          <t>6,93; 22,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,01; 20,82</t>
+          <t>9,13; 20,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,48; 21,04</t>
+          <t>8,31; 20,72</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,2; 16,39</t>
+          <t>4,85; 17,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 23,09</t>
+          <t>4,88; 22,41</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,68; 18,3</t>
+          <t>9,59; 18,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,87; 21,39</t>
+          <t>11,46; 21,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,39; 14,22</t>
+          <t>5,73; 14,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,85; 19,03</t>
+          <t>6,66; 19,09</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,58; 19,79</t>
+          <t>11,11; 19,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,32; 18,91</t>
+          <t>10,27; 18,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 18,71</t>
+          <t>10,41; 18,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,68; 56,92</t>
+          <t>11,84; 51,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 19,2</t>
+          <t>10,77; 19,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,98; 16,35</t>
+          <t>9,04; 15,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 18,06</t>
+          <t>9,86; 18,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,3; 25,75</t>
+          <t>11,9; 24,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12,27; 18,12</t>
+          <t>11,87; 17,73</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,61; 16,14</t>
+          <t>10,49; 16,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,28; 17,02</t>
+          <t>11,23; 16,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 36,37</t>
+          <t>13,9; 39,73</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,28; 33,39</t>
+          <t>19,15; 33,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,13; 24,98</t>
+          <t>14,04; 25,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,39; 20,47</t>
+          <t>10,7; 20,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,58; 30,22</t>
+          <t>14,88; 30,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,87; 24,09</t>
+          <t>12,28; 23,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,45; 22,44</t>
+          <t>11,7; 22,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 20,54</t>
+          <t>10,35; 20,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>8,99; 35,59</t>
+          <t>9,16; 39,6</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,17; 25,48</t>
+          <t>17,0; 25,56</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,63; 22,0</t>
+          <t>14,32; 22,01</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,53; 18,82</t>
+          <t>11,6; 18,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,14; 29,32</t>
+          <t>13,28; 29,01</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,08; 27,68</t>
+          <t>12,53; 27,23</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,82; 21,87</t>
+          <t>6,51; 22,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,25; 27,02</t>
+          <t>10,24; 26,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 13,5</t>
+          <t>3,09; 14,13</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,98; 11,04</t>
+          <t>2,0; 12,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,41; 24,85</t>
+          <t>10,99; 26,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,08; 24,06</t>
+          <t>7,51; 22,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,71; 16,24</t>
+          <t>3,21; 15,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 18,05</t>
+          <t>8,78; 17,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>11,02; 21,53</t>
+          <t>10,83; 21,24</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,57; 21,96</t>
+          <t>10,99; 21,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,09</t>
+          <t>4,16; 12,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>13,94; 18,99</t>
+          <t>14,03; 18,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,37</t>
+          <t>14,42; 19,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,72; 16,37</t>
+          <t>11,82; 16,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,54; 29,37</t>
+          <t>12,95; 29,33</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,13</t>
+          <t>11,74; 15,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,11; 15,35</t>
+          <t>10,98; 15,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,48; 15,2</t>
+          <t>10,73; 15,06</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,33; 18,89</t>
+          <t>11,23; 18,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,46; 16,6</t>
+          <t>13,39; 16,6</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,3; 16,45</t>
+          <t>13,31; 16,66</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,84; 14,9</t>
+          <t>11,78; 14,86</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,0; 21,74</t>
+          <t>12,9; 22,08</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8536; 19547</t>
+          <t>8552; 19942</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10823; 23795</t>
+          <t>10233; 22881</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7515; 19277</t>
+          <t>7258; 19064</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7286; 18476</t>
+          <t>7083; 18009</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9058; 20093</t>
+          <t>8740; 19615</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3942; 12311</t>
+          <t>3798; 12459</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8451; 19799</t>
+          <t>8717; 20347</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8449; 21716</t>
+          <t>8513; 23025</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20121; 35869</t>
+          <t>19994; 35257</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17191; 31878</t>
+          <t>16815; 31728</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19248; 35285</t>
+          <t>19366; 34982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18381; 35022</t>
+          <t>18394; 36114</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5333; 15629</t>
+          <t>4969; 14304</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8751; 20437</t>
+          <t>9284; 21348</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5685; 15805</t>
+          <t>5821; 15854</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7876; 19126</t>
+          <t>8012; 19214</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5014; 14227</t>
+          <t>4837; 14509</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5315; 15725</t>
+          <t>5583; 15469</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5117; 15365</t>
+          <t>4911; 14476</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8840; 21228</t>
+          <t>8344; 21225</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12245; 25948</t>
+          <t>12413; 26121</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16794; 31673</t>
+          <t>17196; 31940</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12296; 27488</t>
+          <t>12255; 25599</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19845; 36020</t>
+          <t>19271; 35782</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4822; 13478</t>
+          <t>5085; 13222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9489; 20537</t>
+          <t>9609; 21290</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2541; 10484</t>
+          <t>2599; 10316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3203; 10876</t>
+          <t>3458; 11379</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8812; 20368</t>
+          <t>8933; 19955</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6972; 17306</t>
+          <t>6838; 17040</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2971; 11602</t>
+          <t>3432; 12506</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3077; 14577</t>
+          <t>3082; 14150</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15732; 29743</t>
+          <t>15589; 29870</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19405; 34973</t>
+          <t>18731; 34339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6932; 18271</t>
+          <t>7360; 18426</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7746; 21512</t>
+          <t>7529; 21584</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22190; 37923</t>
+          <t>21302; 37824</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19653; 35992</t>
+          <t>19555; 35249</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22775; 38865</t>
+          <t>21630; 39251</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24985; 121787</t>
+          <t>25332; 111113</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20082; 36302</t>
+          <t>20353; 36370</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18921; 34436</t>
+          <t>19048; 33150</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20551; 36680</t>
+          <t>20024; 36875</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26147; 54751</t>
+          <t>25306; 51784</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>46718; 68992</t>
+          <t>45197; 67506</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42557; 64702</t>
+          <t>42064; 64691</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46337; 69920</t>
+          <t>46143; 68295</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>58255; 155143</t>
+          <t>59299; 169472</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>18308; 33443</t>
+          <t>19181; 33177</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19561; 34595</t>
+          <t>19448; 35716</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13597; 26795</t>
+          <t>14005; 27441</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17108; 35464</t>
+          <t>17460; 35699</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15655; 29299</t>
+          <t>14930; 28316</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15071; 29526</t>
+          <t>15397; 29398</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13886; 27742</t>
+          <t>13975; 27541</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14349; 56779</t>
+          <t>14617; 63170</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>38084; 56509</t>
+          <t>37713; 56691</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>39516; 59414</t>
+          <t>38682; 59431</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30675; 50054</t>
+          <t>30842; 49648</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36388; 81175</t>
+          <t>36771; 80319</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8644; 19801</t>
+          <t>8964; 19480</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3402; 10911</t>
+          <t>3247; 11246</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5812; 15315</t>
+          <t>5804; 15252</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2280; 9303</t>
+          <t>2132; 9734</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1302; 7253</t>
+          <t>1313; 7903</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7151; 17062</t>
+          <t>7544; 17874</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5254; 15644</t>
+          <t>4882; 14896</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1906; 11441</t>
+          <t>2259; 10978</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12055; 24780</t>
+          <t>12047; 24633</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13070; 25522</t>
+          <t>12845; 25188</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12860; 26719</t>
+          <t>13377; 26257</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5792; 16845</t>
+          <t>5796; 17690</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>84470; 115104</t>
+          <t>85011; 114520</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90892; 122054</t>
+          <t>90882; 122061</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>73616; 102829</t>
+          <t>74234; 101623</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>81275; 190321</t>
+          <t>83927; 190055</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>75476; 104569</t>
+          <t>76129; 102688</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>74191; 102489</t>
+          <t>73357; 102622</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>70178; 101803</t>
+          <t>71865; 100885</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>83306; 138880</t>
+          <t>82566; 137795</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>168876; 208258</t>
+          <t>167929; 208235</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172629; 213536</t>
+          <t>172768; 216285</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>153613; 193312</t>
+          <t>152826; 192781</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>179830; 300741</t>
+          <t>178450; 305421</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP2003-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP2003-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>15,11%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,8%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15,27%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>13,88%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>19,71%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16,48%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>15,11%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,8%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>15,27%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 20,69</t>
+          <t>9,75; 22,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 27,46</t>
+          <t>4,72; 15,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 24,68</t>
+          <t>9,49; 22,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 17,44</t>
+          <t>6,58; 16,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 21,4</t>
+          <t>8,8; 20,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,6; 15,08</t>
+          <t>13,3; 28,45</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,67; 22,57</t>
+          <t>9,81; 25,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 16,92</t>
+          <t>6,78; 18,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>10,63; 18,75</t>
+          <t>10,52; 18,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10,13; 19,12</t>
+          <t>10,23; 19,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,57; 20,9</t>
+          <t>11,56; 21,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 15,09</t>
+          <t>7,98; 15,4</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,83%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>10,31%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>14,69%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>11,58%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>16,48%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>10,15%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,83%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,31%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,09; 17,53</t>
+          <t>6,13; 17,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 24,61</t>
+          <t>5,7; 16,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,96; 16,23</t>
+          <t>4,55; 13,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8,46; 20,29</t>
+          <t>9,14; 22,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 17,61</t>
+          <t>6,51; 19,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,06; 16,8</t>
+          <t>10,97; 24,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65; 13,72</t>
+          <t>5,62; 15,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,95; 22,76</t>
+          <t>8,2; 20,88</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,57; 15,93</t>
+          <t>7,3; 15,41</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,62; 17,86</t>
+          <t>9,61; 17,41</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,03; 12,6</t>
+          <t>6,32; 13,15</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,25; 19,04</t>
+          <t>9,96; 18,87</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>14,21%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>14,16%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>9,27%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>13,02%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>17,8%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9,46%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,63%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>14,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>9,27%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,86; 20,44</t>
+          <t>9,4; 21,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 26,2</t>
+          <t>8,77; 21,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,5; 17,88</t>
+          <t>5,04; 17,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,93; 22,79</t>
+          <t>4,71; 22,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>9,13; 20,4</t>
+          <t>7,37; 20,95</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,31; 20,72</t>
+          <t>11,81; 25,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,85; 17,66</t>
+          <t>4,21; 18,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,88; 22,41</t>
+          <t>6,21; 22,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 18,38</t>
+          <t>9,84; 18,66</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 21,0</t>
+          <t>11,96; 21,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,73; 14,34</t>
+          <t>5,7; 14,19</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 19,09</t>
+          <t>6,85; 18,6</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>14,46%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>13,45%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16,85%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>15,17%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>14,25%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>14,19%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>14,46%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>12,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,45%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,11; 19,73</t>
+          <t>10,6; 18,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,27; 18,52</t>
+          <t>8,64; 16,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,89</t>
+          <t>9,85; 17,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 51,93</t>
+          <t>12,07; 23,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,77; 19,24</t>
+          <t>11,36; 19,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 15,74</t>
+          <t>10,37; 18,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,86; 18,15</t>
+          <t>10,84; 18,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,9; 24,36</t>
+          <t>11,18; 22,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,87; 17,73</t>
+          <t>12,05; 17,93</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,13</t>
+          <t>10,63; 16,25</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 16,62</t>
+          <t>11,07; 16,87</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,9; 39,73</t>
+          <t>12,75; 20,62</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>17,67%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>15,84%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>25,18%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>19,21%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>15,09%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>21,27%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>17,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>16,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>19,15; 33,12</t>
+          <t>12,86; 23,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,04; 25,79</t>
+          <t>11,55; 22,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 20,96</t>
+          <t>10,36; 21,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14,88; 30,42</t>
+          <t>8,35; 32,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,28; 23,28</t>
+          <t>18,39; 32,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,7; 22,34</t>
+          <t>14,14; 25,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,35; 20,39</t>
+          <t>10,39; 20,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9,16; 39,6</t>
+          <t>13,24; 26,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 25,56</t>
+          <t>17,11; 25,98</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,32; 22,01</t>
+          <t>14,2; 22,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11,6; 18,67</t>
+          <t>11,59; 19,15</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,28; 29,01</t>
+          <t>12,66; 27,11</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,05%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14,05%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>19,55%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>13,25%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>17,39%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7,03%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,05%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,53; 27,23</t>
+          <t>2,0; 11,06</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>6,51; 22,54</t>
+          <t>10,94; 24,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10,24; 26,91</t>
+          <t>7,3; 21,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 14,13</t>
+          <t>3,01; 16,32</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,0; 12,02</t>
+          <t>12,94; 28,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 26,03</t>
+          <t>6,95; 23,4</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,51; 22,91</t>
+          <t>10,22; 27,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 15,58</t>
+          <t>3,2; 14,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 17,95</t>
+          <t>8,63; 18,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,83; 21,24</t>
+          <t>10,56; 22,02</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10,99; 21,58</t>
+          <t>10,64; 21,58</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,16; 12,7</t>
+          <t>4,18; 11,81</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13,7%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>13,06%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,8%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>13,85%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>16,42%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>16,75%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>13,88%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>17,35%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>13,06%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>12,8%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,03; 18,9</t>
+          <t>11,64; 15,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>14,42; 19,37</t>
+          <t>11,1; 15,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,18</t>
+          <t>10,79; 15,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,95; 29,33</t>
+          <t>11,24; 18,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,84</t>
+          <t>14,11; 18,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,98; 15,37</t>
+          <t>14,37; 19,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,73; 15,06</t>
+          <t>11,67; 16,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11,23; 18,75</t>
+          <t>11,85; 16,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13,39; 16,6</t>
+          <t>13,47; 16,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,31; 16,66</t>
+          <t>13,31; 16,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11,78; 14,86</t>
+          <t>11,78; 15,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,9; 22,08</t>
+          <t>12,2; 16,44</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13854</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13764</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>13184</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>13380</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>16425</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>12729</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11880</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13854</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>7276</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13764</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>14185</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>26065</t>
+          <t>25324</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8552; 19942</t>
+          <t>8935; 21036</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10233; 22881</t>
+          <t>3897; 12572</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7258; 19064</t>
+          <t>8557; 20031</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7083; 18009</t>
+          <t>8019; 20432</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8740; 19615</t>
+          <t>8481; 19591</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3798; 12459</t>
+          <t>11084; 23711</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8717; 20347</t>
+          <t>7575; 19338</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8513; 23025</t>
+          <t>6905; 18460</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19994; 35257</t>
+          <t>19791; 35312</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16815; 31728</t>
+          <t>16979; 32328</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>19366; 34982</t>
+          <t>19354; 36151</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18394; 36114</t>
+          <t>17858; 34467</t>
         </is>
       </c>
     </row>
@@ -2004,37 +2004,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8919</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9495</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>13157</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9443</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>14293</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>9914</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12855</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8919</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>9495</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8851</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>13970</t>
+          <t>13013</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>26825</t>
+          <t>26170</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4969; 14304</t>
+          <t>5047; 14262</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9284; 21348</t>
+          <t>5248; 14910</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5821; 15854</t>
+          <t>4802; 14395</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8012; 19214</t>
+          <t>8183; 19722</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4837; 14509</t>
+          <t>5313; 15610</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5583; 15469</t>
+          <t>9514; 21008</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4911; 14476</t>
+          <t>5491; 15516</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8344; 21225</t>
+          <t>7912; 20160</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>12413; 26121</t>
+          <t>11969; 25268</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17196; 31940</t>
+          <t>17176; 31131</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>12255; 25599</t>
+          <t>12834; 26728</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19271; 35782</t>
+          <t>18531; 35119</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>13896</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>11645</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6566</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>6190</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>8418</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>14459</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>5458</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6305</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>13896</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11645</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>6566</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7231</t>
+          <t>6372</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13537</t>
+          <t>12562</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5085; 13222</t>
+          <t>9194; 20879</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>9609; 21290</t>
+          <t>7213; 17496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2599; 10316</t>
+          <t>3567; 12187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3458; 11379</t>
+          <t>2657; 12886</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8933; 19955</t>
+          <t>4767; 13552</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6838; 17040</t>
+          <t>9593; 20822</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3432; 12506</t>
+          <t>2429; 10701</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3082; 14150</t>
+          <t>3199; 11523</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15589; 29870</t>
+          <t>15990; 30327</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18731; 34339</t>
+          <t>19556; 34634</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7360; 18426</t>
+          <t>7327; 18243</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7529; 21584</t>
+          <t>7393; 20078</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>27339</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>25581</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>27327</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>33248</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>29075</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>27134</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>29482</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>51580</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>27339</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>25581</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>27327</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36515</t>
+          <t>28132</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88095</t>
+          <t>61380</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>21302; 37824</t>
+          <t>20029; 35444</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19555; 35249</t>
+          <t>18189; 34138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21630; 39251</t>
+          <t>20009; 36267</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>25332; 111113</t>
+          <t>23822; 46602</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20353; 36370</t>
+          <t>21780; 38143</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19048; 33150</t>
+          <t>19740; 35387</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>20024; 36875</t>
+          <t>22530; 38880</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25306; 51784</t>
+          <t>19615; 39277</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45197; 67506</t>
+          <t>45885; 68268</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42064; 64691</t>
+          <t>42634; 65139</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>46143; 68295</t>
+          <t>45466; 69312</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>59299; 169472</t>
+          <t>47524; 76872</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>21490</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>21571</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>20081</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>23091</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>25228</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>26607</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>19748</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>24954</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>21490</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21571</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>20081</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>22333</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>51903</t>
+          <t>45424</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19181; 33177</t>
+          <t>15637; 28302</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>19448; 35716</t>
+          <t>15191; 30019</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14005; 27441</t>
+          <t>13994; 28717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17460; 35699</t>
+          <t>12170; 46886</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14930; 28316</t>
+          <t>18423; 32872</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15397; 29398</t>
+          <t>19573; 35655</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13975; 27541</t>
+          <t>13602; 26990</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>14617; 63170</t>
+          <t>15498; 30625</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>37713; 56691</t>
+          <t>37943; 57629</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38682; 59431</t>
+          <t>38343; 59409</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>30842; 49648</t>
+          <t>30815; 50941</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>36771; 80319</t>
+          <t>33257; 71230</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3320</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11663</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>9134</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>5052</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>13982</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>6614</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>9853</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4841</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3320</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>11663</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>9134</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10343</t>
+          <t>10031</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8964; 19480</t>
+          <t>1315; 7269</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3247; 11246</t>
+          <t>7509; 17162</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5804; 15252</t>
+          <t>4745; 14275</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2132; 9734</t>
+          <t>2016; 10943</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1313; 7903</t>
+          <t>9257; 20086</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7544; 17874</t>
+          <t>3466; 11674</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4882; 14896</t>
+          <t>5794; 15845</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2259; 10978</t>
+          <t>2250; 10052</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12047; 24633</t>
+          <t>11843; 24935</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12845; 25188</t>
+          <t>12521; 26107</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13377; 26257</t>
+          <t>12949; 26257</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5796; 17690</t>
+          <t>5746; 16234</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>150</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>123</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>119</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>88819</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>87231</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>85723</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>93922</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>99526</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>105530</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>87184</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>112415</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>88819</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>87231</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>85723</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>104352</t>
+          <t>86970</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>216767</t>
+          <t>180892</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>85011; 114520</t>
+          <t>75464; 103661</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>90882; 122061</t>
+          <t>74151; 103249</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74234; 101623</t>
+          <t>72270; 101759</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>83927; 190055</t>
+          <t>76181; 126383</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>76129; 102688</t>
+          <t>85495; 114933</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>73357; 102622</t>
+          <t>90566; 122555</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>71865; 100885</t>
+          <t>73286; 103329</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>82566; 137795</t>
+          <t>72613; 102459</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>167929; 208235</t>
+          <t>168982; 211297</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>172768; 216285</t>
+          <t>172765; 215132</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>152826; 192781</t>
+          <t>152927; 195427</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>178450; 305421</t>
+          <t>157537; 212203</t>
         </is>
       </c>
     </row>
